--- a/test_students_10.xlsx
+++ b/test_students_10.xlsx
@@ -484,34 +484,34 @@
         <v>2026</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="L2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="R2" t="str">
-        <v>85.11</v>
+        <v>96.44</v>
       </c>
       <c r="S2" t="str">
         <v>PASS</v>
@@ -543,34 +543,34 @@
         <v>2026</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K3">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M3">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="R3" t="str">
-        <v>96.44</v>
+        <v>83.11</v>
       </c>
       <c r="S3" t="str">
         <v>PASS</v>
@@ -602,34 +602,34 @@
         <v>2026</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="J4">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K4">
         <v>93</v>
       </c>
       <c r="L4">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M4">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="O4">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="R4" t="str">
-        <v>94.00</v>
+        <v>93.78</v>
       </c>
       <c r="S4" t="str">
         <v>PASS</v>
@@ -661,34 +661,34 @@
         <v>2026</v>
       </c>
       <c r="I5">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L5">
+        <v>45</v>
+      </c>
+      <c r="M5">
+        <v>90</v>
+      </c>
+      <c r="N5">
         <v>43</v>
       </c>
-      <c r="M5">
-        <v>86</v>
-      </c>
-      <c r="N5">
-        <v>46</v>
-      </c>
       <c r="O5">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="R5" t="str">
-        <v>98.00</v>
+        <v>108.44</v>
       </c>
       <c r="S5" t="str">
         <v>PASS</v>
@@ -720,34 +720,34 @@
         <v>2026</v>
       </c>
       <c r="I6">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>39</v>
       </c>
       <c r="K6">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M6">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="R6" t="str">
-        <v>99.11</v>
+        <v>84.44</v>
       </c>
       <c r="S6" t="str">
         <v>PASS</v>
@@ -779,34 +779,34 @@
         <v>2026</v>
       </c>
       <c r="I7">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
         <v>43</v>
       </c>
-      <c r="K7">
-        <v>80</v>
-      </c>
       <c r="L7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="N7">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="R7" t="str">
-        <v>91.33</v>
+        <v>93.33</v>
       </c>
       <c r="S7" t="str">
         <v>PASS</v>
@@ -838,34 +838,34 @@
         <v>2026</v>
       </c>
       <c r="I8">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K8">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="L8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M8">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="N8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="R8" t="str">
-        <v>76.89</v>
+        <v>83.78</v>
       </c>
       <c r="S8" t="str">
         <v>PASS</v>
@@ -897,34 +897,34 @@
         <v>2026</v>
       </c>
       <c r="I9">
+        <v>68</v>
+      </c>
+      <c r="J9">
+        <v>38</v>
+      </c>
+      <c r="K9">
+        <v>86</v>
+      </c>
+      <c r="L9">
+        <v>31</v>
+      </c>
+      <c r="M9">
+        <v>87</v>
+      </c>
+      <c r="N9">
+        <v>49</v>
+      </c>
+      <c r="O9">
         <v>69</v>
-      </c>
-      <c r="J9">
-        <v>34</v>
-      </c>
-      <c r="K9">
-        <v>56</v>
-      </c>
-      <c r="L9">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>42</v>
-      </c>
-      <c r="N9">
-        <v>30</v>
-      </c>
-      <c r="O9">
-        <v>87</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>350</v>
+        <v>428</v>
       </c>
       <c r="R9" t="str">
-        <v>77.78</v>
+        <v>95.11</v>
       </c>
       <c r="S9" t="str">
         <v>PASS</v>
@@ -956,34 +956,34 @@
         <v>2026</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K10">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L10">
         <v>37</v>
       </c>
       <c r="M10">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="N10">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="O10">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="R10" t="str">
-        <v>86.22</v>
+        <v>93.33</v>
       </c>
       <c r="S10" t="str">
         <v>PASS</v>
@@ -1015,34 +1015,34 @@
         <v>2026</v>
       </c>
       <c r="I11">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J11">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K11">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="L11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M11">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="N11">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="O11">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="R11" t="str">
-        <v>92.44</v>
+        <v>74.00</v>
       </c>
       <c r="S11" t="str">
         <v>PASS</v>
